--- a/Input/urbs_intertemporal_2050/2040.xlsx
+++ b/Input/urbs_intertemporal_2050/2040.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\Input\urbs_intertemporal_2050\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{264BD064-AA44-4247-ADD5-25D82E2D36BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEBE4DAB-C77A-4BA8-A55B-88E1C25EDDC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="-1935" windowWidth="29040" windowHeight="17520" tabRatio="796" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" tabRatio="796" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="97">
   <si>
     <t>Property</t>
   </si>
@@ -181,9 +181,6 @@
     <t>Coal Plant</t>
   </si>
   <si>
-    <t>Coal Lignite</t>
-  </si>
-  <si>
     <t>Gas Plant (CCGT)</t>
   </si>
   <si>
@@ -319,36 +316,44 @@
     <t>EU27.Gas plant</t>
   </si>
   <si>
-    <t>Coal CCUS</t>
-  </si>
-  <si>
-    <t>Coal Lignite CCUS</t>
-  </si>
-  <si>
     <t>Gas Plant (CCGT) CCUS</t>
   </si>
   <si>
-    <t>Piped Gas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LNG </t>
-  </si>
-  <si>
-    <t>Gas Plant (CCGT) LNG</t>
+    <t>Gas</t>
+  </si>
+  <si>
+    <t>Oil</t>
+  </si>
+  <si>
+    <t>Slack</t>
+  </si>
+  <si>
+    <t>Lignite Plant</t>
+  </si>
+  <si>
+    <t>Other non-res</t>
+  </si>
+  <si>
+    <t>Oil Plant</t>
+  </si>
+  <si>
+    <t>Coal Plant CCUS</t>
+  </si>
+  <si>
+    <t>Lignite Plant CCUS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="#,##0.000"/>
     <numFmt numFmtId="168" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="29">
     <font>
@@ -540,7 +545,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -738,12 +743,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1259,7 +1258,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="168" fontId="20" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1390,13 +1389,11 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1404,20 +1401,18 @@
     <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="363">
     <cellStyle name="20% - Akzent1" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1784,132 +1779,943 @@
     <cellStyle name="Zelle überprüfen 4" xfId="214" xr:uid="{00000000-0005-0000-0000-0000D6000000}"/>
     <cellStyle name="Zelle überprüfen 5" xfId="215" xr:uid="{00000000-0005-0000-0000-0000D7000000}"/>
   </cellStyles>
-  <dxfs count="15">
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
+  <dxfs count="105">
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <border>
@@ -2259,7 +3065,7 @@
       <c r="A3" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="66">
+      <c r="B3" s="64">
         <v>15000000</v>
       </c>
       <c r="C3" s="29" t="s">
@@ -2289,10 +3095,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="15" customFormat="1">
       <c r="A1" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -2307,7 +3113,7 @@
       <c r="A3" s="5">
         <v>1</v>
       </c>
-      <c r="B3" s="65">
+      <c r="B3" s="63">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2315,7 +3121,7 @@
       <c r="A4" s="5">
         <v>2</v>
       </c>
-      <c r="B4" s="65">
+      <c r="B4" s="63">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2323,7 +3129,7 @@
       <c r="A5" s="5">
         <v>3</v>
       </c>
-      <c r="B5" s="65">
+      <c r="B5" s="63">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2331,7 +3137,7 @@
       <c r="A6" s="5">
         <v>4</v>
       </c>
-      <c r="B6" s="65">
+      <c r="B6" s="63">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2339,7 +3145,7 @@
       <c r="A7" s="5">
         <v>5</v>
       </c>
-      <c r="B7" s="65">
+      <c r="B7" s="63">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2347,7 +3153,7 @@
       <c r="A8" s="5">
         <v>6</v>
       </c>
-      <c r="B8" s="65">
+      <c r="B8" s="63">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2355,7 +3161,7 @@
       <c r="A9" s="5">
         <v>7</v>
       </c>
-      <c r="B9" s="65">
+      <c r="B9" s="63">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2363,7 +3169,7 @@
       <c r="A10" s="5">
         <v>8</v>
       </c>
-      <c r="B10" s="65">
+      <c r="B10" s="63">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2371,7 +3177,7 @@
       <c r="A11" s="5">
         <v>9</v>
       </c>
-      <c r="B11" s="65">
+      <c r="B11" s="63">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2379,7 +3185,7 @@
       <c r="A12" s="5">
         <v>10</v>
       </c>
-      <c r="B12" s="65">
+      <c r="B12" s="63">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2387,7 +3193,7 @@
       <c r="A13" s="5">
         <v>11</v>
       </c>
-      <c r="B13" s="65">
+      <c r="B13" s="63">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2395,7 +3201,7 @@
       <c r="A14" s="5">
         <v>12</v>
       </c>
-      <c r="B14" s="65">
+      <c r="B14" s="63">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2419,13 +3225,13 @@
   <sheetData>
     <row r="1" spans="1:3" s="15" customFormat="1">
       <c r="A1" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="15" t="s">
         <v>85</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -2444,13 +3250,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -2502,7 +3308,7 @@
   <sheetPr>
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.6640625" style="3" customWidth="1"/>
@@ -2605,7 +3411,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>21</v>
@@ -2705,13 +3511,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>21</v>
       </c>
       <c r="D10">
-        <v>36.54</v>
+        <v>32.04</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>22</v>
@@ -2720,11 +3526,34 @@
         <v>22</v>
       </c>
     </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11">
+        <v>32.04</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B8:B10">
-    <cfRule type="expression" dxfId="14" priority="1">
+  <conditionalFormatting sqref="B8:B11">
+    <cfRule type="expression" dxfId="104" priority="1">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B11">
+    <cfRule type="duplicateValues" dxfId="103" priority="53"/>
   </conditionalFormatting>
   <dataValidations xWindow="307" yWindow="342" count="3">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Maximum commodity use per hour" prompt="For stock commodities, this value limits the energy use per hour (MW)._x000a_" sqref="F1" xr:uid="{BD7D29D4-B7B6-4AA6-9F21-C9B837F5FDC1}"/>
@@ -2741,7 +3570,7 @@
   <sheetPr>
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.6640625" style="3" customWidth="1"/>
@@ -2806,38 +3635,38 @@
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="49" t="s">
-        <v>40</v>
+      <c r="B2" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="C2" s="20">
         <v>0</v>
       </c>
-      <c r="D2" s="54">
-        <v>46710</v>
+      <c r="D2" s="20">
+        <v>56122</v>
       </c>
       <c r="E2" s="50" t="s">
         <v>22</v>
       </c>
       <c r="F2" s="51">
-        <v>0</v>
-      </c>
-      <c r="G2" s="52">
-        <v>2620279.14</v>
-      </c>
-      <c r="H2" s="52">
-        <v>9143.1016799999998</v>
-      </c>
-      <c r="I2" s="59">
-        <v>0</v>
+        <v>0.5</v>
+      </c>
+      <c r="G2" s="54">
+        <v>1784013.3448000001</v>
+      </c>
+      <c r="H2" s="55">
+        <v>28544.213516799999</v>
+      </c>
+      <c r="I2" s="57">
+        <v>2.7</v>
       </c>
       <c r="J2" s="53">
         <v>0</v>
       </c>
-      <c r="K2" s="60">
+      <c r="K2" s="58">
         <v>7.2999999999999995E-2</v>
       </c>
       <c r="L2" s="53">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="M2" s="28" t="e">
         <v>#N/A</v>
@@ -2847,38 +3676,38 @@
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="49" t="s">
-        <v>41</v>
+      <c r="B3" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="C3" s="20">
         <v>0</v>
       </c>
-      <c r="D3" s="54">
-        <v>59840</v>
+      <c r="D3" s="20">
+        <v>43599</v>
       </c>
       <c r="E3" s="50" t="s">
         <v>22</v>
       </c>
       <c r="F3" s="51">
-        <v>0</v>
-      </c>
-      <c r="G3" s="53">
-        <v>3345037.2</v>
-      </c>
-      <c r="H3" s="53">
-        <v>28432.799999999999</v>
-      </c>
-      <c r="I3" s="61">
-        <v>0.35699999999999998</v>
+        <v>0.65</v>
+      </c>
+      <c r="G3" s="52">
+        <v>2230016.6809999999</v>
+      </c>
+      <c r="H3" s="52">
+        <v>43931.328608800002</v>
+      </c>
+      <c r="I3" s="59">
+        <v>3.2</v>
       </c>
       <c r="J3" s="53">
         <v>0</v>
       </c>
-      <c r="K3" s="60">
+      <c r="K3" s="58">
         <v>7.2999999999999995E-2</v>
       </c>
       <c r="L3" s="53">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="M3" s="28" t="e">
         <v>#N/A</v>
@@ -2888,38 +3717,38 @@
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="49" t="s">
-        <v>42</v>
+      <c r="B4" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="C4" s="20">
         <v>0</v>
       </c>
-      <c r="D4" s="67">
+      <c r="D4" s="20">
         <v>999999</v>
       </c>
       <c r="E4" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="51">
-        <v>0.5</v>
-      </c>
-      <c r="G4" s="56">
-        <v>1784013.3448000001</v>
-      </c>
-      <c r="H4" s="57">
-        <v>28544.213516799999</v>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="52">
+        <v>735908.18400000012</v>
+      </c>
+      <c r="H4" s="52">
+        <v>16725.186000000002</v>
       </c>
       <c r="I4" s="59">
-        <v>2.7</v>
-      </c>
-      <c r="J4" s="53">
+        <v>2.6</v>
+      </c>
+      <c r="J4" s="54">
         <v>0</v>
       </c>
-      <c r="K4" s="60">
+      <c r="K4" s="58">
         <v>7.2999999999999995E-2</v>
       </c>
       <c r="L4" s="53">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="M4" s="28" t="e">
         <v>#N/A</v>
@@ -2929,38 +3758,38 @@
       <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="49" t="s">
-        <v>43</v>
+      <c r="B5" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="C5" s="20">
         <v>0</v>
       </c>
-      <c r="D5" s="67">
-        <v>999999</v>
+      <c r="D5" s="20">
+        <v>13483</v>
       </c>
       <c r="E5" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="51">
-        <v>0.65</v>
-      </c>
-      <c r="G5" s="52">
-        <v>2230016.6809999999</v>
-      </c>
-      <c r="H5" s="52">
-        <v>43931.328608800002</v>
-      </c>
-      <c r="I5" s="61">
-        <v>3.2</v>
-      </c>
-      <c r="J5" s="53">
+      <c r="F5" s="3">
         <v>0</v>
       </c>
-      <c r="K5" s="60">
-        <v>7.2999999999999995E-2</v>
+      <c r="G5">
+        <v>5648000</v>
+      </c>
+      <c r="H5" s="65">
+        <v>16725.186000000002</v>
+      </c>
+      <c r="I5">
+        <v>2.6</v>
+      </c>
+      <c r="J5" s="54">
+        <v>0</v>
+      </c>
+      <c r="K5" s="43">
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="L5" s="53">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="M5" s="28" t="e">
         <v>#N/A</v>
@@ -2970,35 +3799,35 @@
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="49" t="s">
-        <v>44</v>
+      <c r="B6" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="C6" s="20">
         <v>0</v>
       </c>
-      <c r="D6" s="67">
-        <v>999999</v>
+      <c r="D6" s="20">
+        <v>14578</v>
       </c>
       <c r="E6" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="51">
-        <v>0.25</v>
-      </c>
-      <c r="G6" s="52">
-        <v>735908.18400000012</v>
-      </c>
-      <c r="H6" s="52">
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>5648000</v>
+      </c>
+      <c r="H6" s="65">
         <v>16725.186000000002</v>
       </c>
-      <c r="I6" s="61">
+      <c r="I6">
         <v>2.6</v>
       </c>
-      <c r="J6" s="56">
+      <c r="J6" s="54">
         <v>0</v>
       </c>
-      <c r="K6" s="60">
-        <v>7.2999999999999995E-2</v>
+      <c r="K6" s="43">
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="L6" s="53">
         <v>25</v>
@@ -3011,38 +3840,38 @@
       <c r="A7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="49" t="s">
-        <v>45</v>
+      <c r="B7" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="C7" s="20">
         <v>0</v>
       </c>
-      <c r="D7" s="55">
-        <v>94200</v>
+      <c r="D7" s="20">
+        <v>100000</v>
       </c>
       <c r="E7" s="50" t="s">
         <v>22</v>
       </c>
       <c r="F7" s="51">
+        <v>0.5</v>
+      </c>
+      <c r="G7" s="53">
+        <v>3222374.1032400001</v>
+      </c>
+      <c r="H7" s="53">
+        <v>61882.96289200001</v>
+      </c>
+      <c r="I7" s="59">
+        <v>6.29</v>
+      </c>
+      <c r="J7" s="54">
         <v>0</v>
       </c>
-      <c r="G7" s="52">
-        <v>5296308.9000000004</v>
-      </c>
-      <c r="H7" s="57">
-        <v>120421.3392</v>
-      </c>
-      <c r="I7" s="59">
-        <v>8.5</v>
-      </c>
-      <c r="J7" s="53">
-        <v>0</v>
-      </c>
-      <c r="K7" s="60">
-        <v>7.2999999999999995E-2</v>
+      <c r="K7" s="43">
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="L7" s="53">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="M7" s="28" t="e">
         <v>#N/A</v>
@@ -3052,38 +3881,38 @@
       <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="49" t="s">
-        <v>46</v>
+      <c r="B8" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="C8" s="20">
         <v>0</v>
       </c>
       <c r="D8" s="20">
-        <v>999999999999</v>
+        <v>100000</v>
       </c>
       <c r="E8" s="50" t="s">
         <v>22</v>
       </c>
       <c r="F8" s="51">
+        <v>0.65</v>
+      </c>
+      <c r="G8" s="53">
+        <v>3623777.1062800004</v>
+      </c>
+      <c r="H8" s="53">
+        <v>68684.513765600001</v>
+      </c>
+      <c r="I8" s="59">
+        <v>4.7</v>
+      </c>
+      <c r="J8" s="54">
         <v>0</v>
       </c>
-      <c r="G8" s="58">
-        <v>5648000</v>
-      </c>
-      <c r="H8" s="58">
-        <v>0</v>
-      </c>
-      <c r="I8" s="62">
-        <v>53.2</v>
-      </c>
-      <c r="J8" s="53">
-        <v>0</v>
-      </c>
-      <c r="K8" s="60">
-        <v>7.2999999999999995E-2</v>
+      <c r="K8" s="43">
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="L8" s="53">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="M8" s="28" t="e">
         <v>#N/A</v>
@@ -3093,38 +3922,38 @@
       <c r="A9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="49" t="s">
-        <v>89</v>
+      <c r="B9" s="3" t="s">
+        <v>88</v>
       </c>
       <c r="C9" s="20">
         <v>0</v>
       </c>
-      <c r="D9" s="55">
-        <v>0</v>
+      <c r="D9" s="20">
+        <v>100000</v>
       </c>
       <c r="E9" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="51">
-        <v>0.5</v>
+      <c r="F9" s="3">
+        <v>0</v>
       </c>
       <c r="G9" s="53">
-        <v>3222374.1032400001</v>
+        <v>1672518.6</v>
       </c>
       <c r="H9" s="53">
-        <v>61882.96289200001</v>
-      </c>
-      <c r="I9" s="61">
-        <v>6.29</v>
-      </c>
-      <c r="J9" s="56">
+        <v>39025.4</v>
+      </c>
+      <c r="I9" s="59">
+        <v>3.2</v>
+      </c>
+      <c r="J9" s="54">
         <v>0</v>
       </c>
       <c r="K9" s="43">
         <v>7.0999999999999994E-2</v>
       </c>
       <c r="L9" s="53">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="M9" s="28" t="e">
         <v>#N/A</v>
@@ -3135,37 +3964,37 @@
         <v>9</v>
       </c>
       <c r="B10" s="49" t="s">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="C10" s="20">
         <v>0</v>
       </c>
-      <c r="D10" s="55">
-        <v>0</v>
+      <c r="D10" s="20">
+        <v>94198</v>
       </c>
       <c r="E10" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="51">
-        <v>0.65</v>
-      </c>
-      <c r="G10" s="53">
-        <v>3623777.1062800004</v>
-      </c>
-      <c r="H10" s="53">
-        <v>68684.513765600001</v>
-      </c>
-      <c r="I10" s="61">
-        <v>4.7</v>
-      </c>
-      <c r="J10" s="56">
+      <c r="F10" s="3">
         <v>0</v>
       </c>
-      <c r="K10" s="43">
-        <v>7.0999999999999994E-2</v>
+      <c r="G10" s="52">
+        <v>5296308.9000000004</v>
+      </c>
+      <c r="H10" s="55">
+        <v>120421.3392</v>
+      </c>
+      <c r="I10" s="57">
+        <v>8.5</v>
+      </c>
+      <c r="J10" s="53">
+        <v>0</v>
+      </c>
+      <c r="K10" s="58">
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="L10" s="53">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="M10" s="28" t="e">
         <v>#N/A</v>
@@ -3176,37 +4005,37 @@
         <v>9</v>
       </c>
       <c r="B11" s="49" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="C11" s="20">
         <v>0</v>
       </c>
-      <c r="D11" s="55">
-        <v>0</v>
+      <c r="D11" s="20">
+        <v>46703</v>
       </c>
       <c r="E11" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="51">
-        <v>0.25</v>
-      </c>
-      <c r="G11" s="53">
-        <v>1672518.6</v>
-      </c>
-      <c r="H11" s="53">
-        <v>39025.4</v>
-      </c>
-      <c r="I11" s="61">
-        <v>3.2</v>
-      </c>
-      <c r="J11" s="56">
+      <c r="F11" s="3">
         <v>0</v>
       </c>
-      <c r="K11" s="43">
-        <v>7.0999999999999994E-2</v>
+      <c r="G11" s="52">
+        <v>2620279.14</v>
+      </c>
+      <c r="H11" s="52">
+        <v>9143.1016799999998</v>
+      </c>
+      <c r="I11" s="57">
+        <v>0</v>
+      </c>
+      <c r="J11" s="53">
+        <v>0</v>
+      </c>
+      <c r="K11" s="58">
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="L11" s="53">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="M11" s="28" t="e">
         <v>#N/A</v>
@@ -3216,77 +4045,163 @@
       <c r="A12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="63" t="s">
-        <v>94</v>
+      <c r="B12" s="49" t="s">
+        <v>41</v>
       </c>
       <c r="C12" s="20">
         <v>0</v>
       </c>
-      <c r="D12" s="67">
-        <v>999999</v>
+      <c r="D12" s="20">
+        <v>61218</v>
       </c>
       <c r="E12" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="51">
-        <v>0.25</v>
-      </c>
-      <c r="G12" s="52">
-        <v>735908.18400000012</v>
-      </c>
-      <c r="H12" s="52">
-        <v>16725.186000000002</v>
-      </c>
-      <c r="I12" s="61">
-        <v>2.6</v>
-      </c>
-      <c r="J12" s="56">
+      <c r="F12" s="3">
         <v>0</v>
       </c>
-      <c r="K12" s="60">
+      <c r="G12" s="53">
+        <v>3345037.2</v>
+      </c>
+      <c r="H12" s="53">
+        <v>28432.799999999999</v>
+      </c>
+      <c r="I12" s="59">
+        <v>0.35699999999999998</v>
+      </c>
+      <c r="J12" s="53">
+        <v>0</v>
+      </c>
+      <c r="K12" s="58">
         <v>7.2999999999999995E-2</v>
       </c>
       <c r="L12" s="53">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M12" s="28" t="e">
         <v>#N/A</v>
       </c>
     </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="20">
+        <v>0</v>
+      </c>
+      <c r="D13" s="20">
+        <v>999999</v>
+      </c>
+      <c r="E13" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="56">
+        <v>5648000</v>
+      </c>
+      <c r="H13" s="56">
+        <v>0</v>
+      </c>
+      <c r="I13" s="60">
+        <v>53.2</v>
+      </c>
+      <c r="J13" s="53">
+        <v>0</v>
+      </c>
+      <c r="K13" s="58">
+        <v>7.2999999999999995E-2</v>
+      </c>
+      <c r="L13" s="53">
+        <v>25</v>
+      </c>
+      <c r="M13" s="28" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L1" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
-  <conditionalFormatting sqref="A2:A12 B2:B3 C2:C12 P2:XFD4">
-    <cfRule type="expression" dxfId="13" priority="3">
+  <conditionalFormatting sqref="P2:XFD4">
+    <cfRule type="expression" dxfId="101" priority="31">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:F3 A4:C4 E4:F4">
-    <cfRule type="expression" dxfId="12" priority="16">
+  <conditionalFormatting sqref="A1:XFD1 A14:F15 J14:XFD15 A16:XFD1048576 N13:XFD13">
+    <cfRule type="expression" dxfId="100" priority="48">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:XFD1 A13:F15 J13:XFD15 A16:XFD1048576">
-    <cfRule type="expression" dxfId="11" priority="20">
+  <conditionalFormatting sqref="N12:XFD12">
+    <cfRule type="expression" dxfId="96" priority="32">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B12">
-    <cfRule type="expression" dxfId="10" priority="1">
+  <conditionalFormatting sqref="C2:D13 F9:F13 F4:F6">
+    <cfRule type="expression" dxfId="80" priority="13">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="9" priority="11">
+  <conditionalFormatting sqref="E2:E4 E12:E13">
+    <cfRule type="expression" dxfId="79" priority="12">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:I2">
-    <cfRule type="expression" dxfId="8" priority="10">
+  <conditionalFormatting sqref="F2">
+    <cfRule type="expression" dxfId="78" priority="11">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N12:XFD12">
-    <cfRule type="expression" dxfId="7" priority="4">
+  <conditionalFormatting sqref="F7">
+    <cfRule type="expression" dxfId="77" priority="10">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B9">
+    <cfRule type="expression" dxfId="76" priority="9">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A4">
+    <cfRule type="expression" dxfId="75" priority="8">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A13">
+    <cfRule type="expression" dxfId="74" priority="7">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10">
+    <cfRule type="expression" dxfId="73" priority="6">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:B12">
+    <cfRule type="expression" dxfId="72" priority="5">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:B12">
+    <cfRule type="expression" dxfId="71" priority="4">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="expression" dxfId="70" priority="3">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2">
+    <cfRule type="expression" dxfId="69" priority="2">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G11:I11">
+    <cfRule type="expression" dxfId="68" priority="1">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3313,7 +4228,7 @@
   <sheetPr>
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -3333,24 +4248,24 @@
         <v>11</v>
       </c>
       <c r="C1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="E1" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="18" t="s">
-        <v>49</v>
-      </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="63" t="s">
-        <v>43</v>
+      <c r="A2" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D2" s="24">
         <v>1</v>
@@ -3360,16 +4275,16 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="63" t="s">
-        <v>43</v>
+      <c r="A3" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="64">
+        <v>50</v>
+      </c>
+      <c r="D3" s="62">
         <v>0.43</v>
       </c>
       <c r="E3" s="24" t="e">
@@ -3378,14 +4293,14 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="63" t="s">
-        <v>43</v>
+      <c r="A4" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D4" s="24">
         <v>0.36299999999999999</v>
@@ -3395,14 +4310,14 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="63" t="s">
-        <v>44</v>
+      <c r="A5" s="61" t="s">
+        <v>43</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D5" s="24">
         <v>1</v>
@@ -3412,16 +4327,16 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="63" t="s">
-        <v>44</v>
+      <c r="A6" s="61" t="s">
+        <v>43</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="64">
+        <v>50</v>
+      </c>
+      <c r="D6" s="62">
         <v>0.62</v>
       </c>
       <c r="E6" s="24" t="e">
@@ -3430,14 +4345,14 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="63" t="s">
-        <v>44</v>
+      <c r="A7" s="61" t="s">
+        <v>43</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D7" s="48">
         <v>0.125</v>
@@ -3448,14 +4363,14 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="63" t="s">
-        <v>46</v>
+      <c r="A8" s="61" t="s">
+        <v>45</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D8" s="24">
         <v>1</v>
@@ -3466,14 +4381,14 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="63" t="s">
-        <v>46</v>
+      <c r="A9" s="61" t="s">
+        <v>45</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" s="24">
         <v>0.35</v>
@@ -3484,14 +4399,14 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="63" t="s">
-        <v>46</v>
+      <c r="A10" s="61" t="s">
+        <v>45</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D10" s="24">
         <v>0</v>
@@ -3502,14 +4417,14 @@
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="63" t="s">
-        <v>45</v>
+      <c r="A11" s="61" t="s">
+        <v>44</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D11" s="24">
         <v>1</v>
@@ -3520,14 +4435,14 @@
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="63" t="s">
-        <v>45</v>
+      <c r="A12" s="61" t="s">
+        <v>44</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D12" s="24">
         <v>0.38</v>
@@ -3538,14 +4453,14 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="63" t="s">
+      <c r="A13" s="61" t="s">
         <v>42</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D13" s="24">
         <v>1</v>
@@ -3555,16 +4470,16 @@
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="63" t="s">
+      <c r="A14" s="61" t="s">
         <v>42</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="64">
+        <v>50</v>
+      </c>
+      <c r="D14" s="62">
         <v>0.47</v>
       </c>
       <c r="E14" s="24" t="e">
@@ -3573,14 +4488,14 @@
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="63" t="s">
+      <c r="A15" s="61" t="s">
         <v>42</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" s="24">
         <v>0.34179999999999999</v>
@@ -3591,14 +4506,14 @@
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="63" t="s">
+      <c r="A16" s="61" t="s">
         <v>40</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" s="24">
         <v>1</v>
@@ -3609,14 +4524,14 @@
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="63" t="s">
+      <c r="A17" s="61" t="s">
         <v>40</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D17" s="24">
         <v>1</v>
@@ -3627,14 +4542,14 @@
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="63" t="s">
+      <c r="A18" s="61" t="s">
         <v>41</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D18" s="24">
         <v>1</v>
@@ -3645,14 +4560,14 @@
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="63" t="s">
+      <c r="A19" s="61" t="s">
         <v>41</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D19" s="24">
         <v>1</v>
@@ -3663,14 +4578,14 @@
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="63" t="s">
-        <v>89</v>
+      <c r="A20" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D20" s="24">
         <v>1</v>
@@ -3681,35 +4596,35 @@
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="63" t="s">
-        <v>89</v>
+      <c r="A21" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D21" s="24">
-        <v>0.38</v>
+        <v>0.34</v>
       </c>
       <c r="E21" s="24" t="e">
-        <f>D21*E19</f>
+        <f>D21*E18</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="63" t="s">
-        <v>89</v>
+      <c r="A22" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D22" s="24">
-        <v>3.4180000000000002E-2</v>
+        <v>3.6299999999999999E-2</v>
       </c>
       <c r="E22" s="24" t="e">
         <f>D22*E20</f>
@@ -3717,68 +4632,67 @@
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="63" t="s">
-        <v>90</v>
+      <c r="A23" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D23" s="24">
         <v>1</v>
       </c>
-      <c r="E23" s="24" t="e">
+      <c r="E23" s="24">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="24">
+        <v>0.49</v>
+      </c>
+      <c r="E24" s="24" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="63" t="s">
-        <v>90</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D24" s="24">
-        <v>0.34</v>
-      </c>
-      <c r="E24" s="24" t="e">
-        <f>D24*E21</f>
-        <v>#N/A</v>
-      </c>
-    </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="63" t="s">
-        <v>90</v>
+      <c r="A25" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D25" s="24">
-        <v>3.6299999999999999E-2</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="E25" s="24" t="e">
-        <f>D25*E23</f>
+        <f>NA()</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="63" t="s">
-        <v>91</v>
+      <c r="A26" s="61" t="s">
+        <v>88</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D26" s="24">
         <v>1</v>
@@ -3788,17 +4702,17 @@
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="63" t="s">
-        <v>91</v>
+      <c r="A27" s="61" t="s">
+        <v>88</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D27" s="24">
-        <v>0.49</v>
+        <v>50</v>
+      </c>
+      <c r="D27" s="62">
+        <v>0.62</v>
       </c>
       <c r="E27" s="24" t="e">
         <f>NA()</f>
@@ -3806,52 +4720,53 @@
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="63" t="s">
-        <v>91</v>
+      <c r="A28" s="61" t="s">
+        <v>88</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D28" s="24">
-        <v>1.2500000000000001E-2</v>
-      </c>
-      <c r="E28" s="24" t="e">
-        <f>NA()</f>
-        <v>#N/A</v>
+        <v>50</v>
+      </c>
+      <c r="D28" s="48">
+        <v>0.125</v>
+      </c>
+      <c r="E28" s="24">
+        <f>D28*E26</f>
+        <v>0.15</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="63" t="s">
-        <v>94</v>
+      <c r="A29" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D29" s="24">
         <v>1</v>
       </c>
-      <c r="E29" s="24">
-        <v>1.2</v>
+      <c r="E29" s="24" t="e">
+        <f>D29*E27</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="63" t="s">
-        <v>94</v>
+      <c r="A30" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D30" s="64">
-        <v>0.62</v>
+        <v>50</v>
+      </c>
+      <c r="D30" s="24">
+        <v>0.4</v>
       </c>
       <c r="E30" s="24" t="e">
         <f>NA()</f>
@@ -3859,49 +4774,105 @@
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="63" t="s">
-        <v>94</v>
+      <c r="A31" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D31" s="48">
-        <v>0.125</v>
-      </c>
-      <c r="E31" s="24">
-        <f>D31*E29</f>
-        <v>0.15</v>
+        <v>50</v>
+      </c>
+      <c r="D31" s="24">
+        <v>0.26700000000000002</v>
+      </c>
+      <c r="E31" s="24" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D32" s="24">
+        <v>1</v>
+      </c>
+      <c r="E32" s="24" t="e">
+        <f>D32*E30</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D33" s="24">
+        <v>0.4</v>
+      </c>
+      <c r="E33" s="24" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D34" s="24">
+        <v>0.26700000000000002</v>
+      </c>
+      <c r="E34" s="24" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A30:C31 E30:E31 A2:C4 E2:XFD19">
-    <cfRule type="expression" dxfId="6" priority="5">
+  <conditionalFormatting sqref="A2:C4 E2:XFD19 A30:C31 E30:E31">
+    <cfRule type="expression" dxfId="67" priority="133">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:E29">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="66" priority="129">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:XFD1 A5 C5 A6:C19">
-    <cfRule type="expression" dxfId="4" priority="23">
+    <cfRule type="expression" dxfId="65" priority="151">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A20:XFD25 A26 C26:XFD26 A27:XFD28 F29:XFD31 A32:XFD1048576">
-    <cfRule type="expression" dxfId="3" priority="6">
+  <conditionalFormatting sqref="A20:XFD25 A26 C26:XFD26 A27:XFD28 F29:XFD31 A32:XFD33 A35:XFD1048576 F34:XFD34">
+    <cfRule type="expression" dxfId="64" priority="134">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D5 D8:D13 D15:D19 D2">
-    <cfRule type="expression" dxfId="2" priority="13">
+  <conditionalFormatting sqref="D2 D4:D5 D8:D13 D15:D19">
+    <cfRule type="expression" dxfId="63" priority="141">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
-    <cfRule type="dataBar" priority="22">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4">
+    <cfRule type="dataBar" priority="144">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -3909,8 +4880,8 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D8:D10 D5 D2 E2:E7">
-    <cfRule type="dataBar" priority="20">
+  <conditionalFormatting sqref="D4:D5 D8:D13 D15:D19 D2">
+    <cfRule type="dataBar" priority="150">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -3918,8 +4889,8 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4">
-    <cfRule type="dataBar" priority="16">
+  <conditionalFormatting sqref="D8:D10 D5 D2 E2:E7">
+    <cfRule type="dataBar" priority="148">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -3928,7 +4899,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D13 D15">
-    <cfRule type="dataBar" priority="14">
+    <cfRule type="dataBar" priority="142">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -3937,7 +4908,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15">
-    <cfRule type="dataBar" priority="12">
+    <cfRule type="dataBar" priority="140">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -3946,7 +4917,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D17">
-    <cfRule type="dataBar" priority="19">
+    <cfRule type="dataBar" priority="147">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -3955,7 +4926,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18:D19">
-    <cfRule type="dataBar" priority="18">
+    <cfRule type="dataBar" priority="146">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -3964,7 +4935,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D29">
-    <cfRule type="dataBar" priority="4">
+    <cfRule type="dataBar" priority="132">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -3978,7 +4949,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:E1">
-    <cfRule type="dataBar" priority="45">
+    <cfRule type="dataBar" priority="173">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -3987,14 +4958,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D20:E28">
-    <cfRule type="dataBar" priority="7">
+    <cfRule type="dataBar" priority="135">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
         <color rgb="FF638EC6"/>
       </dataBar>
     </cfRule>
-    <cfRule type="dataBar" priority="8">
+    <cfRule type="dataBar" priority="136">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -4003,7 +4974,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D29:E29 E30:E31">
-    <cfRule type="dataBar" priority="3">
+    <cfRule type="dataBar" priority="131">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -4016,63 +4987,542 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D32:E1048576">
+  <conditionalFormatting sqref="D32:E33 D35:E1048576">
+    <cfRule type="dataBar" priority="180">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8:E10">
+    <cfRule type="dataBar" priority="156">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E11:E12">
+    <cfRule type="dataBar" priority="159">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13:E15">
+    <cfRule type="dataBar" priority="154">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E16:E17">
+    <cfRule type="dataBar" priority="153">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E18:E19">
+    <cfRule type="dataBar" priority="152">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A34:E34">
+    <cfRule type="expression" dxfId="62" priority="127">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D34:E34">
+    <cfRule type="dataBar" priority="128">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:E1">
+    <cfRule type="expression" dxfId="28" priority="54">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A20:C25 A27:C28 A32:E32">
+    <cfRule type="expression" dxfId="27" priority="53">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:E1">
+    <cfRule type="dataBar" priority="55">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5 A6:C19 D8:E12 B2:C4 D16:E19">
+    <cfRule type="expression" dxfId="26" priority="47">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21:C25 C26 B27:C27">
+    <cfRule type="expression" dxfId="25" priority="44">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B20:C20 A26:A28">
+    <cfRule type="expression" dxfId="24" priority="45">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C5">
+    <cfRule type="expression" dxfId="23" priority="42">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8:D10">
+    <cfRule type="dataBar" priority="51">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{44685B10-3CC8-4B4B-8963-7AB19EAE4537}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8:D12 D16:D19">
+    <cfRule type="dataBar" priority="46">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{CC6C4EBD-7073-4DBB-93B6-ED06594F1A51}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D11:E12">
     <cfRule type="dataBar" priority="52">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
         <color rgb="FF638EC6"/>
       </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8:E10">
-    <cfRule type="dataBar" priority="28">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{0936CF41-762C-47A9-A88C-8427F6E2DCD2}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D16:E17">
+    <cfRule type="dataBar" priority="49">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
         <color rgb="FF638EC6"/>
       </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E11:E12">
-    <cfRule type="dataBar" priority="31">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{73EEDA13-5426-4C37-BB1E-5BE999352875}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D18:E19">
+    <cfRule type="dataBar" priority="48">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
         <color rgb="FF638EC6"/>
       </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E13:E15">
-    <cfRule type="dataBar" priority="26">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{9646CAFB-6A9F-4B47-BD3F-55D2A41BB202}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8:E10">
+    <cfRule type="dataBar" priority="50">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
         <color rgb="FF638EC6"/>
       </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E16:E17">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{70CD747D-A2D0-43D5-95FD-66E16F2C3ECE}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E29:E34">
+    <cfRule type="expression" dxfId="22" priority="41">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B28:C28">
+    <cfRule type="expression" dxfId="21" priority="43">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A4">
+    <cfRule type="expression" dxfId="20" priority="40">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A29:A31">
+    <cfRule type="expression" dxfId="19" priority="39">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A32:A34">
+    <cfRule type="expression" dxfId="18" priority="38">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C29 B30:C30">
+    <cfRule type="expression" dxfId="17" priority="36">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E29">
+    <cfRule type="dataBar" priority="35">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{ACA0C948-5283-4A80-8FC2-92F36D156AF1}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E30">
+    <cfRule type="dataBar" priority="37">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{587D3D68-4F4F-4415-9A9D-58FC1CF97CE8}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E31">
+    <cfRule type="dataBar" priority="34">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{495665A8-F3CC-462F-A39C-37EC9D0BC547}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:C31">
+    <cfRule type="expression" dxfId="16" priority="33">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C32 B33:C33">
+    <cfRule type="expression" dxfId="15" priority="31">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E32">
+    <cfRule type="dataBar" priority="30">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{3A4BC41D-5203-46F5-B2E1-17AF2E98438E}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E33">
+    <cfRule type="dataBar" priority="32">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{FBDEE1C8-A3F9-4082-B46F-4974EBE53C8F}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E34">
+    <cfRule type="dataBar" priority="29">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{67543D24-F38D-4AF8-84C3-F00ECE92DF1C}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34:C34">
+    <cfRule type="expression" dxfId="14" priority="28">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A20:A22">
+    <cfRule type="expression" dxfId="13" priority="27">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23:A25">
+    <cfRule type="expression" dxfId="12" priority="26">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D29:D34">
+    <cfRule type="expression" dxfId="11" priority="24">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D29:D34">
+    <cfRule type="dataBar" priority="23">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{8B833A3D-0A35-480F-9DA2-981DAC2A143D}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D29:D34">
     <cfRule type="dataBar" priority="25">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
         <color rgb="FF638EC6"/>
       </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E18:E19">
-    <cfRule type="dataBar" priority="24">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{E307DE49-B9FE-43D4-817E-AC2D1D7CD501}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E27:E28">
+    <cfRule type="expression" dxfId="10" priority="19">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D26:E26">
+    <cfRule type="expression" dxfId="9" priority="16">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D20:E25">
+    <cfRule type="expression" dxfId="8" priority="20">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D26">
+    <cfRule type="dataBar" priority="18">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
         <color rgb="FF638EC6"/>
       </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{DD9D74B1-54B3-4770-A637-C18B717E2CE1}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D20:E25">
+    <cfRule type="dataBar" priority="21">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+    <cfRule type="dataBar" priority="22">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D26:E26 E27:E28">
+    <cfRule type="dataBar" priority="17">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{6F6E52F1-9759-4FAD-BF22-387A01AA6533}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E4">
+    <cfRule type="expression" dxfId="7" priority="11">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2 D4">
+    <cfRule type="expression" dxfId="6" priority="12">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4">
+    <cfRule type="dataBar" priority="13">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4 D2">
+    <cfRule type="dataBar" priority="15">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E4 D2">
+    <cfRule type="dataBar" priority="14">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:E7">
+    <cfRule type="expression" dxfId="5" priority="7">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5">
+    <cfRule type="expression" dxfId="4" priority="8">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5">
+    <cfRule type="dataBar" priority="10">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:E7 D5">
+    <cfRule type="dataBar" priority="9">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13:E15">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13 D15">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13 D15">
+    <cfRule type="dataBar" priority="5">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13 D15">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D15">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13:E15">
+    <cfRule type="dataBar" priority="6">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Ratio at minimum operation point" prompt="Input/Output ratio at point of minimum operation (min-fract in 'Process' sheet)._x000a__x000a_All values have to be larger/equal to ratio!" sqref="E1" xr:uid="{00000000-0002-0000-0400-000000000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Ratio (1)" prompt="Input/output quantities, relative to process throughput" sqref="D1" xr:uid="{00000000-0002-0000-0400-000001000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Ratio at minimum operation point" prompt="Input/Output ratio at point of minimum operation (min-fract in 'Process' sheet)._x000a__x000a_All values have to be larger/equal to ratio!" sqref="E1" xr:uid="{9AF89829-84BB-4CB5-A37D-A07F8C977BBB}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Ratio (1)" prompt="Input/output quantities, relative to process throughput" sqref="D1" xr:uid="{3EE3DD4D-CF4E-4A63-ADB1-2B561D551C08}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -4109,6 +5559,246 @@
           </x14:cfRule>
           <xm:sqref>D29:E29 E30:E31</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{44685B10-3CC8-4B4B-8963-7AB19EAE4537}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D8:D10</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{CC6C4EBD-7073-4DBB-93B6-ED06594F1A51}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D8:D12 D16:D19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{0936CF41-762C-47A9-A88C-8427F6E2DCD2}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D11:E12</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{73EEDA13-5426-4C37-BB1E-5BE999352875}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D16:E17</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{9646CAFB-6A9F-4B47-BD3F-55D2A41BB202}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D18:E19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{70CD747D-A2D0-43D5-95FD-66E16F2C3ECE}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E8:E10</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{ACA0C948-5283-4A80-8FC2-92F36D156AF1}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E29</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{587D3D68-4F4F-4415-9A9D-58FC1CF97CE8}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E30</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{495665A8-F3CC-462F-A39C-37EC9D0BC547}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E31</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{3A4BC41D-5203-46F5-B2E1-17AF2E98438E}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E32</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{FBDEE1C8-A3F9-4082-B46F-4974EBE53C8F}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E33</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{67543D24-F38D-4AF8-84C3-F00ECE92DF1C}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E34</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{8B833A3D-0A35-480F-9DA2-981DAC2A143D}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D29:D34</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{E307DE49-B9FE-43D4-817E-AC2D1D7CD501}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D29:D34</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{DD9D74B1-54B3-4770-A637-C18B717E2CE1}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D26</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{6F6E52F1-9759-4FAD-BF22-387A01AA6533}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D26:E26 E27:E28</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>
@@ -4139,19 +5829,19 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" t="s">
         <v>52</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>53</v>
-      </c>
-      <c r="C1" t="s">
-        <v>54</v>
       </c>
       <c r="D1" t="s">
         <v>11</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F1" s="17" t="s">
         <v>33</v>
@@ -4175,13 +5865,13 @@
         <v>38</v>
       </c>
       <c r="M1" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N1" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="O1" s="16" t="s">
         <v>57</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -4243,46 +5933,46 @@
         <v>10</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D1" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="F1" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="G1" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="H1" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="I1" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="J1" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="K1" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="L1" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="M1" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="N1" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="O1" s="16" t="s">
         <v>70</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>71</v>
       </c>
       <c r="P1" s="16" t="s">
         <v>37</v>
@@ -4291,13 +5981,13 @@
         <v>38</v>
       </c>
       <c r="R1" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="S1" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="S1" s="16" t="s">
+      <c r="T1" s="36" t="s">
         <v>73</v>
-      </c>
-      <c r="T1" s="36" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -4305,7 +5995,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C2" s="39" t="s">
         <v>18</v>
@@ -4365,7 +6055,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C3" s="39" t="s">
         <v>18</v>
@@ -4426,7 +6116,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C4" s="39" t="s">
         <v>18</v>
@@ -4539,19 +6229,19 @@
         <v>11</v>
       </c>
       <c r="C1" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="D1" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1" s="17" t="s">
+      <c r="F1" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="G1" s="17" t="s">
         <v>80</v>
-      </c>
-      <c r="G1" s="17" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -4594,10 +6284,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:2">
